--- a/data/raw/returns/Audio Array.xlsx
+++ b/data/raw/returns/Audio Array.xlsx
@@ -12702,7 +12702,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>405-9316299-5823523</t>
+          <t>405-3372664-3710705</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>LPNCJB1X148070</t>
+          <t>LPNCJB1X148074</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>405-3372664-3710705</t>
+          <t>405-9316299-5823523</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>LPNCJB1X148074</t>
+          <t>LPNCJB1X148070</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>

--- a/data/raw/returns/Audio Array.xlsx
+++ b/data/raw/returns/Audio Array.xlsx
@@ -13730,7 +13730,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>405-3372664-3710705</t>
+          <t>405-9316299-5823523</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>LPNCJB1X148074</t>
+          <t>LPNCJB1X148070</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>405-9316299-5823523</t>
+          <t>405-3372664-3710705</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>LPNCJB1X148070</t>
+          <t>LPNCJB1X148074</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>

--- a/data/raw/returns/Audio Array.xlsx
+++ b/data/raw/returns/Audio Array.xlsx
@@ -13730,7 +13730,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>405-9316299-5823523</t>
+          <t>405-3372664-3710705</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>LPNCJB1X148070</t>
+          <t>LPNCJB1X148074</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>405-3372664-3710705</t>
+          <t>405-9316299-5823523</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>LPNCJB1X148074</t>
+          <t>LPNCJB1X148070</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>

--- a/data/raw/returns/Audio Array.xlsx
+++ b/data/raw/returns/Audio Array.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L458"/>
+  <dimension ref="A1:L457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26266,62 +26266,6 @@
       </c>
       <c r="L457" t="inlineStr"/>
     </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>2026-05-05T12:18:16+00:00</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>171-1115972-5601153</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>FBA79830</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>B0FJ8TSQK1</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>X002CZVYE5</t>
-        </is>
-      </c>
-      <c r="F458" t="inlineStr">
-        <is>
-          <t>Audio Array Singing Bundle | Condenser Mic with Boom Arm &amp; Sound Card V8 | Voice Effects, Reverb, Bluetooth | Ideal for Podcasting, Karaoke, Live Streaming, YouTube &amp; Singing - GB-03</t>
-        </is>
-      </c>
-      <c r="G458" t="n">
-        <v>1</v>
-      </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>AMD2</t>
-        </is>
-      </c>
-      <c r="I458" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J458" t="inlineStr">
-        <is>
-          <t>SWITCHEROO</t>
-        </is>
-      </c>
-      <c r="K458" t="inlineStr">
-        <is>
-          <t>LPNAMD2M3640431</t>
-        </is>
-      </c>
-      <c r="L458" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/returns/Audio Array.xlsx
+++ b/data/raw/returns/Audio Array.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L458"/>
+  <dimension ref="A1:L454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>405-9316299-5823523</t>
+          <t>405-3372664-3710705</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>LPNCJB1X148070</t>
+          <t>LPNCJB1X148074</t>
         </is>
       </c>
       <c r="L394" t="inlineStr"/>
@@ -22730,7 +22730,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>405-3372664-3710705</t>
+          <t>405-9316299-5823523</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>LPNCJB1X148074</t>
+          <t>LPNCJB1X148070</t>
         </is>
       </c>
       <c r="L395" t="inlineStr"/>
@@ -26097,230 +26097,6 @@
         </is>
       </c>
       <c r="L454" t="inlineStr"/>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>2026-05-06T05:33:10+00:00</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>403-7731096-1918707</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>FBA79974</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>B0GD8JSPB1</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>X002HC9D9L</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>Audio Array 60W Bluetooth Bookshelf Speaker Pair | 1.5" Silk Dome Tweeter, 4" Sub Woofer | Music &amp; Monitor Mode | Aux, HDMI, USB-C, TRS &amp; RCA Connectivity</t>
-        </is>
-      </c>
-      <c r="G455" t="n">
-        <v>1</v>
-      </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>BOM5</t>
-        </is>
-      </c>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J455" t="inlineStr">
-        <is>
-          <t>UNDELIVERABLE_REFUSED</t>
-        </is>
-      </c>
-      <c r="K455" t="inlineStr">
-        <is>
-          <t>LPNBOM5F5211889</t>
-        </is>
-      </c>
-      <c r="L455" t="inlineStr"/>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>2026-05-06T04:47:26+00:00</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>407-2774811-7101927</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>FBA79008</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>B0CH4RT4P8</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>X001W3B0Y7</t>
-        </is>
-      </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>Audio Array AI-06 Streaming Audio Mixer Sound Card | XLR, 1/4" &amp; line in | PC/Phone RGB Mixer with Volume Fader, Individual Control, Mute and Monitoring, 48V Phantom Power | Stream, Podcast &amp; Karaoke</t>
-        </is>
-      </c>
-      <c r="G456" t="n">
-        <v>1</v>
-      </c>
-      <c r="H456" t="inlineStr">
-        <is>
-          <t>BOM5</t>
-        </is>
-      </c>
-      <c r="I456" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J456" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K456" t="inlineStr">
-        <is>
-          <t>LPNBOM5F5243783</t>
-        </is>
-      </c>
-      <c r="L456" t="inlineStr"/>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>2026-05-06T04:02:09+00:00</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>404-1413727-5778733</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>FBA75679</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>B0B4JRQP22</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>X001L5GHUN</t>
-        </is>
-      </c>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>Audio Array AA-02 3-Panel Curved Isolation Shield with Insulation, Absorption &amp; Reflection Filter | 3/8" and 5/8" Universal Mic Mount for Recording Studio, Podcasts, Singing &amp; Broadcasting</t>
-        </is>
-      </c>
-      <c r="G457" t="n">
-        <v>1</v>
-      </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>BOM5</t>
-        </is>
-      </c>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J457" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="K457" t="inlineStr">
-        <is>
-          <t>LPNBOM5F5287183</t>
-        </is>
-      </c>
-      <c r="L457" t="inlineStr"/>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>2026-05-05T20:11:46+00:00</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>404-9057810-8333164</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>FBA79848</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>B0GN97RFPR</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>X002JTXRM1</t>
-        </is>
-      </c>
-      <c r="F458" t="inlineStr">
-        <is>
-          <t>Audio Array AM-S2 | 3.5" Studio Monitor Speaker Pair | 50W RMS with Bluetooth 5.0 | Fiberglass Woofer &amp; 1″ Silk Dome Tweeter, Class-D | TI 3116D2 Amp | TRS/RCA/AUX Inputs, Bass &amp; Treble Control</t>
-        </is>
-      </c>
-      <c r="G458" t="n">
-        <v>1</v>
-      </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>CCX1</t>
-        </is>
-      </c>
-      <c r="I458" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J458" t="inlineStr">
-        <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="K458" t="inlineStr">
-        <is>
-          <t>LPNCCX1B3097502</t>
-        </is>
-      </c>
-      <c r="L458" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/Audio Array.xlsx
+++ b/data/raw/returns/Audio Array.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L454"/>
+  <dimension ref="A1:L453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>405-3372664-3710705</t>
+          <t>405-9316299-5823523</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>LPNCJB1X148074</t>
+          <t>LPNCJB1X148070</t>
         </is>
       </c>
       <c r="L394" t="inlineStr"/>
@@ -22730,7 +22730,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>405-9316299-5823523</t>
+          <t>405-3372664-3710705</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>LPNCJB1X148070</t>
+          <t>LPNCJB1X148074</t>
         </is>
       </c>
       <c r="L395" t="inlineStr"/>
@@ -26041,62 +26041,6 @@
         </is>
       </c>
       <c r="L453" t="inlineStr"/>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>2026-05-06T07:54:00+00:00</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>403-3996650-0283534</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>FBA79005</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>B0CKHVHVQ1</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>X001VS0O1X</t>
-        </is>
-      </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>Audio Array AM-W45 Wireless Conference Microphone with Speaker | Bluetooth, USB &amp; 4 Mics | 360° Pickup Upto 4M | Noise Reduction &amp; Enhanced Voice | Portable Speakerphone for Video Calls/Zoom Meeting</t>
-        </is>
-      </c>
-      <c r="G454" t="n">
-        <v>1</v>
-      </c>
-      <c r="H454" t="inlineStr">
-        <is>
-          <t>HYD8</t>
-        </is>
-      </c>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J454" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K454" t="inlineStr">
-        <is>
-          <t>LPNHYD8EE02504</t>
-        </is>
-      </c>
-      <c r="L454" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/Audio Array.xlsx
+++ b/data/raw/returns/Audio Array.xlsx
@@ -3554,27 +3554,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>406-6095938-9247562</t>
+          <t>406-4803906-5357102</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>X001L4QVU5</t>
+          <t>X002EDSRBN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Audio Array Mic | Podcast Mic XLR Condenser Microphone Kit with Boom Arm | Pop Filter | Shock Mount &amp; 2M Cable | Cardioid Recording Microphone for Streaming | Podcasting &amp; Home Studio | AM-C2</t>
+          <t>Audio Array AH-60-RD Semi-Open Back DJ Headphones | 50mm Drivers Delivers Dynamic Balanced Output | 15Hz-25kHz, 32Ω, 100dB SPL, 1200mW | 3m OFC Single-Sided Cable with Screw-On 3.5mm + 6.3mm Plug</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNDEL5S14658333</t>
+          <t>LPNDEL5S14658334</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3610,27 +3610,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>406-4803906-5357102</t>
+          <t>406-6095938-9247562</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>X002EDSRBN</t>
+          <t>X001L4QVU5</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Audio Array AH-60-RD Semi-Open Back DJ Headphones | 50mm Drivers Delivers Dynamic Balanced Output | 15Hz-25kHz, 32Ω, 100dB SPL, 1200mW | 3m OFC Single-Sided Cable with Screw-On 3.5mm + 6.3mm Plug</t>
+          <t>Audio Array Mic | Podcast Mic XLR Condenser Microphone Kit with Boom Arm | Pop Filter | Shock Mount &amp; 2M Cable | Cardioid Recording Microphone for Streaming | Podcasting &amp; Home Studio | AM-C2</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNDEL5S14658334</t>
+          <t>LPNDEL5S14658333</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -30934,7 +30934,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>405-9316299-5823523</t>
+          <t>405-3372664-3710705</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -30977,7 +30977,7 @@
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>LPNCJB1X148070</t>
+          <t>LPNCJB1X148074</t>
         </is>
       </c>
       <c r="L540" t="inlineStr"/>
@@ -30990,7 +30990,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>405-3372664-3710705</t>
+          <t>405-9316299-5823523</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -31033,7 +31033,7 @@
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t>LPNCJB1X148074</t>
+          <t>LPNCJB1X148070</t>
         </is>
       </c>
       <c r="L541" t="inlineStr"/>

--- a/data/raw/returns/Audio Array.xlsx
+++ b/data/raw/returns/Audio Array.xlsx
@@ -3782,27 +3782,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>406-6095938-9247562</t>
+          <t>406-4803906-5357102</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X001L4QVU5</t>
+          <t>X002EDSRBN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Audio Array Mic | Podcast Mic XLR Condenser Microphone Kit with Boom Arm | Pop Filter | Shock Mount &amp; 2M Cable | Cardioid Recording Microphone for Streaming | Podcasting &amp; Home Studio | AM-C2</t>
+          <t>Audio Array AH-60-RD Semi-Open Back DJ Headphones | 50mm Drivers Delivers Dynamic Balanced Output | 15Hz-25kHz, 32Ω, 100dB SPL, 1200mW | 3m OFC Single-Sided Cable with Screw-On 3.5mm + 6.3mm Plug</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNDEL5S14658333</t>
+          <t>LPNDEL5S14658334</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3838,27 +3838,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>406-4803906-5357102</t>
+          <t>406-6095938-9247562</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>X002EDSRBN</t>
+          <t>X001L4QVU5</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audio Array AH-60-RD Semi-Open Back DJ Headphones | 50mm Drivers Delivers Dynamic Balanced Output | 15Hz-25kHz, 32Ω, 100dB SPL, 1200mW | 3m OFC Single-Sided Cable with Screw-On 3.5mm + 6.3mm Plug</t>
+          <t>Audio Array Mic | Podcast Mic XLR Condenser Microphone Kit with Boom Arm | Pop Filter | Shock Mount &amp; 2M Cable | Cardioid Recording Microphone for Streaming | Podcasting &amp; Home Studio | AM-C2</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNDEL5S14658334</t>
+          <t>LPNDEL5S14658333</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
